--- a/calculos_tramos.xlsx
+++ b/calculos_tramos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\Practicas_Inst2\1_Vapor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Unidades compartidas\Practicas_Inst2\1_Vapor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6974AE-73E3-4C59-83BA-BC44839B9CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3F200D-DDD1-4AB0-82FD-1B524BFB8926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1514,20 +1514,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B5:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>20</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H11" t="s">
         <v>10</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1642,44 +1642,44 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A2:AJ69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="23.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="23.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="AC3" s="15" t="s">
         <v>90</v>
       </c>
       <c r="AD3" s="15"/>
       <c r="AE3" s="15"/>
     </row>
-    <row r="4" spans="1:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:36" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AA4" t="s">
         <v>64</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>9.0579999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA6" t="s">
         <v>67</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>8.8179999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>15</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>8.8979999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>13</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>8.8302962618141159</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>8.7802962618141169</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="E10" s="6"/>
       <c r="P10" s="6"/>
       <c r="AA10" t="s">
@@ -2029,7 +2029,7 @@
         <v>8.7102962618141166</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D11" s="14" t="s">
         <v>16</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>8.6902962618141171</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" ht="16.8" x14ac:dyDescent="0.35">
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="G12" t="s">
@@ -2110,7 +2110,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="H13">
@@ -2140,7 +2140,7 @@
         <v>1.6754499999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="O14" s="6"/>
@@ -2161,7 +2161,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="5" t="s">
@@ -2192,7 +2192,7 @@
         <v>9.9999999999997868E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="O16" s="6"/>
@@ -2215,7 +2215,7 @@
         <v>0.24000000000000021</v>
       </c>
     </row>
-    <row r="17" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="3" t="s">
@@ -2262,7 +2262,7 @@
         <v>0.16000000000000014</v>
       </c>
     </row>
-    <row r="18" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:31" x14ac:dyDescent="0.3">
       <c r="F18" s="3">
         <f>1/I13</f>
         <v>4.6484818058422119</v>
@@ -2313,7 +2313,7 @@
         <v>7.0000000000000284E-2</v>
       </c>
     </row>
-    <row r="19" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>58</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>0.11999999999999922</v>
       </c>
     </row>
-    <row r="20" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:31" x14ac:dyDescent="0.3">
       <c r="AA20" t="s">
         <v>70</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>7.0000000000000284E-2</v>
       </c>
     </row>
-    <row r="21" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AA21" t="s">
         <v>71</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>8.9999999999999858E-2</v>
       </c>
     </row>
-    <row r="22" spans="4:31" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:31" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="4" t="s">
         <v>35</v>
       </c>
@@ -2382,8 +2382,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="4:31" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:31" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
         <v>15</v>
       </c>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="R24" s="5"/>
     </row>
-    <row r="25" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>13</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D26" s="1" t="s">
         <v>14</v>
       </c>
@@ -2474,11 +2474,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:31" x14ac:dyDescent="0.3">
       <c r="E27" s="6"/>
       <c r="P27" s="6"/>
     </row>
-    <row r="28" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
         <v>53</v>
       </c>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P28" s="6"/>
     </row>
-    <row r="29" spans="4:31" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="29" spans="4:31" ht="16.8" x14ac:dyDescent="0.35">
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="G29" t="s">
@@ -2524,7 +2524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:31" x14ac:dyDescent="0.3">
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="H30">
@@ -2554,13 +2554,13 @@
         <v>1.6758700000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
     </row>
-    <row r="32" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="5" t="s">
@@ -2574,13 +2574,13 @@
       </c>
       <c r="R32" s="5"/>
     </row>
-    <row r="33" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
     </row>
-    <row r="34" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="3" t="s">
@@ -2610,7 +2610,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:22" x14ac:dyDescent="0.3">
       <c r="F35" s="3">
         <f>1/I30</f>
         <v>4.6436249994195462</v>
@@ -2644,8 +2644,8 @@
         <v>412.71716340000006</v>
       </c>
     </row>
-    <row r="38" spans="4:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="4:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="4:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="4" t="s">
         <v>37</v>
       </c>
@@ -2653,8 +2653,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="4:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="4:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:22" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="4:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" t="s">
         <v>15</v>
       </c>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="R41" s="5"/>
     </row>
-    <row r="42" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
         <v>13</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D43" s="1" t="s">
         <v>14</v>
       </c>
@@ -2746,11 +2746,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:22" x14ac:dyDescent="0.3">
       <c r="E44" s="6"/>
       <c r="P44" s="6"/>
     </row>
-    <row r="45" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D45" s="6" t="s">
         <v>55</v>
       </c>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="P45" s="6"/>
     </row>
-    <row r="46" spans="4:22" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="46" spans="4:22" ht="16.8" x14ac:dyDescent="0.35">
       <c r="E46" s="6"/>
       <c r="G46" t="s">
         <v>22</v>
@@ -2795,7 +2795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="H47">
@@ -2826,14 +2826,14 @@
         <v>1.6763299999999998E-2</v>
       </c>
     </row>
-    <row r="48" spans="4:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
     </row>
-    <row r="49" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="5" t="s">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="R49" s="5"/>
     </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
     </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="3" t="s">
@@ -2886,7 +2886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F52" s="3">
         <f>1/I47</f>
         <v>4.5320438157996108</v>
@@ -2920,14 +2920,14 @@
         <v>159.10647760000009</v>
       </c>
     </row>
-    <row r="55" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="2:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="2:20" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D56" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="2:20" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:20" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D58" t="s">
         <v>15</v>
       </c>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G58" s="5"/>
     </row>
-    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>13</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D60" s="1" t="s">
         <v>14</v>
       </c>
@@ -2976,16 +2976,16 @@
         <v>220</v>
       </c>
     </row>
-    <row r="61" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:20" x14ac:dyDescent="0.3">
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D62" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="2:20" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:20" ht="16.8" x14ac:dyDescent="0.35">
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -3005,7 +3005,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -3022,12 +3022,12 @@
         <v>1.6763299999999998E-2</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="G66" s="5"/>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -3058,7 +3058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F69" s="3">
         <f>1/I64</f>
         <v>4.4787617119618766</v>
@@ -3092,37 +3092,37 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:AJ83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="23.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="23.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
@@ -3130,7 +3130,7 @@
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" t="s">
         <v>29</v>
@@ -3140,13 +3140,13 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>47</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="D6">
@@ -3166,14 +3166,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="I7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AC10" t="s">
         <v>64</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AC12" t="s">
         <v>67</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>15</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>13</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" ht="15.6" x14ac:dyDescent="0.35">
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="H16" t="s">
@@ -3494,7 +3494,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="17" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>16</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>2.4499999999999997</v>
       </c>
     </row>
-    <row r="18" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:36" x14ac:dyDescent="0.3">
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
@@ -3580,7 +3580,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -3591,7 +3591,7 @@
       <c r="Q19" s="14"/>
       <c r="V19" s="7"/>
     </row>
-    <row r="20" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:36" ht="16.8" x14ac:dyDescent="0.35">
       <c r="B20" s="6"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -3648,7 +3648,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="6"/>
@@ -3698,7 +3698,7 @@
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="6"/>
@@ -3736,7 +3736,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="23" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="6"/>
@@ -3764,7 +3764,7 @@
         <v>0.14000000000000012</v>
       </c>
     </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:36" x14ac:dyDescent="0.3">
       <c r="AC24" t="s">
         <v>68</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:36" x14ac:dyDescent="0.3">
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="F25" s="3" t="s">
@@ -3828,7 +3828,7 @@
         <v>8.0000000000000071E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:36" x14ac:dyDescent="0.3">
       <c r="F26" s="3">
         <f>1/L21</f>
         <v>2.1693997487835093</v>
@@ -3883,7 +3883,7 @@
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.3">
       <c r="AC27" t="s">
         <v>71</v>
       </c>
@@ -3898,8 +3898,8 @@
         <v>6.0000000000000053E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="2:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:36" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="2:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="4" t="s">
         <v>35</v>
       </c>
@@ -3907,8 +3907,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:36" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" t="s">
         <v>15</v>
       </c>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="S33" s="5"/>
     </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>13</v>
       </c>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C35" s="1" t="s">
         <v>14</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="3:25" ht="18" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:25" ht="15.6" x14ac:dyDescent="0.35">
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="H36" t="s">
@@ -4012,7 +4012,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C37" s="14" t="s">
         <v>16</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
@@ -4061,7 +4061,7 @@
       <c r="Q38" s="14"/>
       <c r="V38" s="7"/>
     </row>
-    <row r="39" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
@@ -4071,7 +4071,7 @@
       <c r="Q39" s="14"/>
       <c r="V39" s="7"/>
     </row>
-    <row r="40" spans="3:25" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:25" ht="16.2" x14ac:dyDescent="0.3">
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
@@ -4115,7 +4115,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C41" s="2"/>
       <c r="D41" s="6"/>
       <c r="H41">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="V41" s="7"/>
     </row>
-    <row r="42" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C42" s="2"/>
       <c r="D42" s="6"/>
       <c r="J42" s="7"/>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="2"/>
       <c r="D43" s="6"/>
       <c r="F43" s="5" t="s">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="S43" s="5"/>
     </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="F45" s="3" t="s">
@@ -4215,7 +4215,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="F46" s="3">
         <f>1/L41</f>
         <v>2.0319545167300976</v>
@@ -4257,8 +4257,8 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="3:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="3:25" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C49" s="4" t="s">
         <v>37</v>
       </c>
@@ -4266,8 +4266,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="3:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:25" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" t="s">
         <v>15</v>
       </c>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="S51" s="5"/>
     </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
         <v>13</v>
       </c>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C53" s="1" t="s">
         <v>14</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="3:25" ht="18" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:25" ht="15.6" x14ac:dyDescent="0.35">
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
       <c r="H54" t="s">
@@ -4371,7 +4371,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C55" s="14" t="s">
         <v>16</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
@@ -4414,7 +4414,7 @@
       <c r="Q56" s="14"/>
       <c r="V56" s="7"/>
     </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
@@ -4424,7 +4424,7 @@
       <c r="Q57" s="14"/>
       <c r="V57" s="7"/>
     </row>
-    <row r="58" spans="3:25" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:25" ht="16.2" x14ac:dyDescent="0.3">
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
@@ -4468,7 +4468,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C59" s="2"/>
       <c r="D59" s="6"/>
       <c r="J59" s="7"/>
@@ -4476,7 +4476,7 @@
       <c r="P59" s="6"/>
       <c r="V59" s="7"/>
     </row>
-    <row r="60" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="2"/>
       <c r="D60" s="6"/>
       <c r="J60" s="7"/>
@@ -4500,7 +4500,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" spans="3:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C61" s="2"/>
       <c r="D61" s="6"/>
       <c r="F61" s="5" t="s">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="S61" s="5"/>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="F63" s="3" t="s">
@@ -4550,7 +4550,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:25" x14ac:dyDescent="0.3">
       <c r="F64" s="3" t="e">
         <f>1/L59</f>
         <v>#DIV/0!</v>
@@ -4584,14 +4584,14 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="3:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="3:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="3:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="70" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C70" t="s">
         <v>15</v>
       </c>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G70" s="5"/>
     </row>
-    <row r="71" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
         <v>13</v>
       </c>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C72" s="1" t="s">
         <v>14</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="3:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:13" ht="15.6" x14ac:dyDescent="0.35">
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="H73" t="s">
@@ -4647,7 +4647,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C74" s="14" t="s">
         <v>16</v>
       </c>
@@ -4665,19 +4665,19 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="75" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
       <c r="E76" s="14"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="3:13" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:13" ht="16.2" x14ac:dyDescent="0.3">
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
       <c r="E77" s="14"/>
@@ -4700,12 +4700,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C78" s="2"/>
       <c r="D78" s="6"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C79" s="2"/>
       <c r="D79" s="6"/>
       <c r="J79" s="7"/>
@@ -4718,7 +4718,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C80" s="2"/>
       <c r="D80" s="6"/>
       <c r="F80" s="5" t="s">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="G80" s="5"/>
     </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C82" s="6"/>
       <c r="D82" s="6"/>
       <c r="F82" s="3" t="s">
@@ -4745,7 +4745,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F83" s="3" t="e">
         <f>1/L78</f>
         <v>#DIV/0!</v>
